--- a/templates/ヒアリングシート.xlsx
+++ b/templates/ヒアリングシート.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hasegawa tomohisa\OneDrive\デスクトップ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hatsu\Desktop\anken-kanri\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B3157EC-1326-4AD7-B452-E0AE71B70B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B41FC6C-D2E9-4F7D-B16A-7F2B4AED5D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8662C76F-D09F-4417-B53D-C9403C0E950B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8662C76F-D09F-4417-B53D-C9403C0E950B}"/>
   </bookViews>
   <sheets>
     <sheet name="nx" sheetId="1" r:id="rId1"/>
@@ -459,7 +459,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,13 +536,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="8.8000000000000007"/>
@@ -717,7 +710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -727,15 +720,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -826,20 +819,50 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -851,40 +874,22 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -943,32 +948,107 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -985,1181 +1065,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>31750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1026" name="Check Box 2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1026"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>50800</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1028" name="Check Box 4" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1028"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>30</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>32</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1029" name="Check Box 5" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1029"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>33</xdr:col>
-          <xdr:colOff>107950</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>34</xdr:col>
-          <xdr:colOff>146050</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1030" name="Check Box 6" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1030"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>36</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>38</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1031" name="Check Box 7" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1031"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>88900</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1034" name="Check Box 10" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1034"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>25</xdr:col>
-          <xdr:colOff>88900</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>26</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1035" name="Check Box 11" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1035"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>12</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>31750</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1036" name="Check Box 12" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1036"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>76200</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>107950</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1037" name="Check Box 13" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1037"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>21</xdr:col>
-          <xdr:colOff>88900</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>22</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1038" name="Check Box 14" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1038"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>16</xdr:col>
-          <xdr:colOff>31750</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>17</xdr:col>
-          <xdr:colOff>57150</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1039" name="Check Box 15" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1039"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>30</xdr:col>
-          <xdr:colOff>12700</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>31</xdr:col>
-          <xdr:colOff>38100</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1040" name="Check Box 16" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1040"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>34</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>35</xdr:col>
-          <xdr:colOff>50800</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>69850</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1041" name="Check Box 17" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1041"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="0" bIns="32004" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="ja-JP" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Meiryo UI"/>
-                  <a:ea typeface="Meiryo UI"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2458,108 +1363,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9745655D-27D2-4B7F-AD94-A9DB69B1F37E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9745655D-27D2-4B7F-AD94-A9DB69B1F37E}">
   <dimension ref="A1:AU657"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="118" width="1.83203125" customWidth="1"/>
+    <col min="1" max="118" width="1.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="76" t="s">
+    <row r="1" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
-      <c r="Z1" s="76"/>
-      <c r="AA1" s="76"/>
-      <c r="AB1" s="76"/>
-      <c r="AC1" s="76"/>
-      <c r="AD1" s="76"/>
-      <c r="AE1" s="76"/>
-      <c r="AF1" s="76"/>
-      <c r="AG1" s="76"/>
-      <c r="AH1" s="76"/>
-      <c r="AI1" s="76"/>
-      <c r="AJ1" s="76"/>
-      <c r="AK1" s="76"/>
-      <c r="AL1" s="76"/>
-      <c r="AM1" s="76"/>
-      <c r="AN1" s="76"/>
-      <c r="AO1" s="76"/>
-      <c r="AP1" s="76"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
+      <c r="W1" s="91"/>
+      <c r="X1" s="91"/>
+      <c r="Y1" s="91"/>
+      <c r="Z1" s="91"/>
+      <c r="AA1" s="91"/>
+      <c r="AB1" s="91"/>
+      <c r="AC1" s="91"/>
+      <c r="AD1" s="91"/>
+      <c r="AE1" s="91"/>
+      <c r="AF1" s="91"/>
+      <c r="AG1" s="91"/>
+      <c r="AH1" s="91"/>
+      <c r="AI1" s="91"/>
+      <c r="AJ1" s="91"/>
+      <c r="AK1" s="91"/>
+      <c r="AL1" s="91"/>
+      <c r="AM1" s="91"/>
+      <c r="AN1" s="91"/>
+      <c r="AO1" s="91"/>
+      <c r="AP1" s="91"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
     </row>
-    <row r="2" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="76"/>
-      <c r="Y2" s="76"/>
-      <c r="Z2" s="76"/>
-      <c r="AA2" s="76"/>
-      <c r="AB2" s="76"/>
-      <c r="AC2" s="76"/>
-      <c r="AD2" s="76"/>
-      <c r="AE2" s="76"/>
-      <c r="AF2" s="76"/>
-      <c r="AG2" s="76"/>
-      <c r="AH2" s="76"/>
-      <c r="AI2" s="76"/>
-      <c r="AJ2" s="76"/>
-      <c r="AK2" s="76"/>
-      <c r="AL2" s="76"/>
-      <c r="AM2" s="76"/>
-      <c r="AN2" s="76"/>
-      <c r="AO2" s="76"/>
-      <c r="AP2" s="76"/>
+    <row r="2" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="91"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="91"/>
+      <c r="R2" s="91"/>
+      <c r="S2" s="91"/>
+      <c r="T2" s="91"/>
+      <c r="U2" s="91"/>
+      <c r="V2" s="91"/>
+      <c r="W2" s="91"/>
+      <c r="X2" s="91"/>
+      <c r="Y2" s="91"/>
+      <c r="Z2" s="91"/>
+      <c r="AA2" s="91"/>
+      <c r="AB2" s="91"/>
+      <c r="AC2" s="91"/>
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="91"/>
+      <c r="AG2" s="91"/>
+      <c r="AH2" s="91"/>
+      <c r="AI2" s="91"/>
+      <c r="AJ2" s="91"/>
+      <c r="AK2" s="91"/>
+      <c r="AL2" s="91"/>
+      <c r="AM2" s="91"/>
+      <c r="AN2" s="91"/>
+      <c r="AO2" s="91"/>
+      <c r="AP2" s="91"/>
       <c r="AQ2" s="1"/>
       <c r="AR2" s="1"/>
     </row>
-    <row r="3" spans="1:44" ht="12.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:44" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2591,23 +1496,23 @@
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
-      <c r="AF3" s="74">
+      <c r="AF3" s="78">
         <v>46206</v>
       </c>
-      <c r="AG3" s="74"/>
-      <c r="AH3" s="74"/>
-      <c r="AI3" s="74"/>
-      <c r="AJ3" s="74"/>
-      <c r="AK3" s="74"/>
-      <c r="AL3" s="74"/>
-      <c r="AM3" s="74"/>
+      <c r="AG3" s="78"/>
+      <c r="AH3" s="78"/>
+      <c r="AI3" s="78"/>
+      <c r="AJ3" s="78"/>
+      <c r="AK3" s="78"/>
+      <c r="AL3" s="78"/>
+      <c r="AM3" s="78"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
       <c r="AP3" s="1"/>
       <c r="AQ3" s="1"/>
       <c r="AR3" s="1"/>
     </row>
-    <row r="4" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
@@ -2618,18 +1523,18 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="79"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="95"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="95"/>
+      <c r="O4" s="95"/>
+      <c r="P4" s="95"/>
+      <c r="Q4" s="95"/>
+      <c r="R4" s="95"/>
       <c r="S4" s="6" t="s">
         <v>2</v>
       </c>
@@ -2641,27 +1546,27 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AA4" s="6"/>
-      <c r="AB4" s="80" t="s">
+      <c r="AB4" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="AC4" s="80"/>
-      <c r="AD4" s="80"/>
-      <c r="AE4" s="80"/>
-      <c r="AF4" s="80"/>
-      <c r="AG4" s="80"/>
-      <c r="AH4" s="80"/>
-      <c r="AI4" s="80"/>
-      <c r="AJ4" s="80"/>
-      <c r="AK4" s="80"/>
-      <c r="AL4" s="80"/>
-      <c r="AM4" s="80"/>
-      <c r="AN4" s="80"/>
-      <c r="AO4" s="80"/>
-      <c r="AP4" s="80"/>
+      <c r="AC4" s="96"/>
+      <c r="AD4" s="96"/>
+      <c r="AE4" s="96"/>
+      <c r="AF4" s="96"/>
+      <c r="AG4" s="96"/>
+      <c r="AH4" s="96"/>
+      <c r="AI4" s="96"/>
+      <c r="AJ4" s="96"/>
+      <c r="AK4" s="96"/>
+      <c r="AL4" s="96"/>
+      <c r="AM4" s="96"/>
+      <c r="AN4" s="96"/>
+      <c r="AO4" s="96"/>
+      <c r="AP4" s="96"/>
       <c r="AQ4" s="1"/>
       <c r="AR4" s="1"/>
     </row>
-    <row r="5" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -2670,16 +1575,16 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95"/>
+      <c r="P5" s="95"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="95"/>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
@@ -2689,25 +1594,25 @@
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
       <c r="AA5" s="6"/>
-      <c r="AB5" s="80"/>
-      <c r="AC5" s="80"/>
-      <c r="AD5" s="80"/>
-      <c r="AE5" s="80"/>
-      <c r="AF5" s="80"/>
-      <c r="AG5" s="80"/>
-      <c r="AH5" s="80"/>
-      <c r="AI5" s="80"/>
-      <c r="AJ5" s="80"/>
-      <c r="AK5" s="80"/>
-      <c r="AL5" s="80"/>
-      <c r="AM5" s="80"/>
-      <c r="AN5" s="80"/>
-      <c r="AO5" s="80"/>
-      <c r="AP5" s="80"/>
+      <c r="AB5" s="96"/>
+      <c r="AC5" s="96"/>
+      <c r="AD5" s="96"/>
+      <c r="AE5" s="96"/>
+      <c r="AF5" s="96"/>
+      <c r="AG5" s="96"/>
+      <c r="AH5" s="96"/>
+      <c r="AI5" s="96"/>
+      <c r="AJ5" s="96"/>
+      <c r="AK5" s="96"/>
+      <c r="AL5" s="96"/>
+      <c r="AM5" s="96"/>
+      <c r="AN5" s="96"/>
+      <c r="AO5" s="96"/>
+      <c r="AP5" s="96"/>
       <c r="AQ5" s="1"/>
       <c r="AR5" s="1"/>
     </row>
-    <row r="6" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
@@ -2718,50 +1623,50 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
-      <c r="I6" s="77" t="s">
+      <c r="I6" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77"/>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
-      <c r="V6" s="77"/>
-      <c r="W6" s="77"/>
-      <c r="X6" s="77"/>
-      <c r="Y6" s="77"/>
-      <c r="Z6" s="77"/>
-      <c r="AA6" s="77"/>
-      <c r="AB6" s="77"/>
-      <c r="AC6" s="77"/>
-      <c r="AD6" s="77"/>
-      <c r="AE6" s="77"/>
-      <c r="AF6" s="78" t="s">
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="92"/>
+      <c r="Q6" s="92"/>
+      <c r="R6" s="92"/>
+      <c r="S6" s="92"/>
+      <c r="T6" s="92"/>
+      <c r="U6" s="92"/>
+      <c r="V6" s="92"/>
+      <c r="W6" s="92"/>
+      <c r="X6" s="92"/>
+      <c r="Y6" s="92"/>
+      <c r="Z6" s="92"/>
+      <c r="AA6" s="92"/>
+      <c r="AB6" s="92"/>
+      <c r="AC6" s="92"/>
+      <c r="AD6" s="92"/>
+      <c r="AE6" s="92"/>
+      <c r="AF6" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="AG6" s="78"/>
-      <c r="AH6" s="78"/>
-      <c r="AI6" s="78"/>
-      <c r="AJ6" s="78"/>
-      <c r="AK6" s="78"/>
-      <c r="AL6" s="75" t="s">
+      <c r="AG6" s="93"/>
+      <c r="AH6" s="93"/>
+      <c r="AI6" s="93"/>
+      <c r="AJ6" s="93"/>
+      <c r="AK6" s="93"/>
+      <c r="AL6" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="AM6" s="75"/>
-      <c r="AN6" s="75"/>
-      <c r="AO6" s="75"/>
-      <c r="AP6" s="75"/>
+      <c r="AM6" s="94"/>
+      <c r="AN6" s="94"/>
+      <c r="AO6" s="94"/>
+      <c r="AP6" s="94"/>
       <c r="AQ6" s="1"/>
       <c r="AR6" s="1"/>
     </row>
-    <row r="7" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2770,456 +1675,456 @@
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77"/>
-      <c r="T7" s="77"/>
-      <c r="U7" s="77"/>
-      <c r="V7" s="77"/>
-      <c r="W7" s="77"/>
-      <c r="X7" s="77"/>
-      <c r="Y7" s="77"/>
-      <c r="Z7" s="77"/>
-      <c r="AA7" s="77"/>
-      <c r="AB7" s="77"/>
-      <c r="AC7" s="77"/>
-      <c r="AD7" s="77"/>
-      <c r="AE7" s="77"/>
-      <c r="AF7" s="78"/>
-      <c r="AG7" s="78"/>
-      <c r="AH7" s="78"/>
-      <c r="AI7" s="78"/>
-      <c r="AJ7" s="78"/>
-      <c r="AK7" s="78"/>
-      <c r="AL7" s="75"/>
-      <c r="AM7" s="75"/>
-      <c r="AN7" s="75"/>
-      <c r="AO7" s="75"/>
-      <c r="AP7" s="75"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="92"/>
+      <c r="Q7" s="92"/>
+      <c r="R7" s="92"/>
+      <c r="S7" s="92"/>
+      <c r="T7" s="92"/>
+      <c r="U7" s="92"/>
+      <c r="V7" s="92"/>
+      <c r="W7" s="92"/>
+      <c r="X7" s="92"/>
+      <c r="Y7" s="92"/>
+      <c r="Z7" s="92"/>
+      <c r="AA7" s="92"/>
+      <c r="AB7" s="92"/>
+      <c r="AC7" s="92"/>
+      <c r="AD7" s="92"/>
+      <c r="AE7" s="92"/>
+      <c r="AF7" s="93"/>
+      <c r="AG7" s="93"/>
+      <c r="AH7" s="93"/>
+      <c r="AI7" s="93"/>
+      <c r="AJ7" s="93"/>
+      <c r="AK7" s="93"/>
+      <c r="AL7" s="94"/>
+      <c r="AM7" s="94"/>
+      <c r="AN7" s="94"/>
+      <c r="AO7" s="94"/>
+      <c r="AP7" s="94"/>
       <c r="AQ7" s="1"/>
       <c r="AR7" s="1"/>
     </row>
-    <row r="8" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="72" t="s">
+    <row r="8" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="43" t="s">
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43" t="s">
+      <c r="F8" s="86"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="43"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="82" t="s">
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="73" t="s">
+      <c r="L8" s="97"/>
+      <c r="M8" s="97"/>
+      <c r="N8" s="97"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="73"/>
-      <c r="S8" s="73"/>
-      <c r="T8" s="73"/>
-      <c r="U8" s="68" t="s">
+      <c r="R8" s="77"/>
+      <c r="S8" s="77"/>
+      <c r="T8" s="77"/>
+      <c r="U8" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="V8" s="68"/>
-      <c r="W8" s="68"/>
-      <c r="X8" s="68"/>
-      <c r="Y8" s="68"/>
-      <c r="Z8" s="69"/>
-      <c r="AA8" s="70" t="s">
+      <c r="V8" s="72"/>
+      <c r="W8" s="72"/>
+      <c r="X8" s="72"/>
+      <c r="Y8" s="72"/>
+      <c r="Z8" s="73"/>
+      <c r="AA8" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="AB8" s="71"/>
+      <c r="AB8" s="75"/>
       <c r="AC8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="AD8" s="6"/>
       <c r="AE8" s="6"/>
-      <c r="AF8" s="75" t="s">
+      <c r="AF8" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="AG8" s="75"/>
-      <c r="AH8" s="75"/>
-      <c r="AI8" s="75"/>
-      <c r="AJ8" s="75"/>
-      <c r="AK8" s="75"/>
-      <c r="AL8" s="75"/>
-      <c r="AM8" s="75"/>
-      <c r="AN8" s="75"/>
-      <c r="AO8" s="75"/>
-      <c r="AP8" s="75"/>
+      <c r="AG8" s="80"/>
+      <c r="AH8" s="80"/>
+      <c r="AI8" s="80"/>
+      <c r="AJ8" s="80"/>
+      <c r="AK8" s="80"/>
+      <c r="AL8" s="80"/>
+      <c r="AM8" s="80"/>
+      <c r="AN8" s="80"/>
+      <c r="AO8" s="80"/>
+      <c r="AP8" s="81"/>
       <c r="AQ8" s="1"/>
       <c r="AR8" s="1"/>
     </row>
-    <row r="9" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="72"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="73"/>
-      <c r="R9" s="73"/>
-      <c r="S9" s="73"/>
-      <c r="T9" s="73"/>
-      <c r="U9" s="68"/>
-      <c r="V9" s="68"/>
-      <c r="W9" s="68"/>
-      <c r="X9" s="68"/>
-      <c r="Y9" s="68"/>
-      <c r="Z9" s="69"/>
-      <c r="AA9" s="70"/>
-      <c r="AB9" s="71"/>
+    <row r="9" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="76"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="89"/>
+      <c r="J9" s="89"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="100"/>
+      <c r="Q9" s="77"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="77"/>
+      <c r="T9" s="77"/>
+      <c r="U9" s="72"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="72"/>
+      <c r="X9" s="72"/>
+      <c r="Y9" s="72"/>
+      <c r="Z9" s="73"/>
+      <c r="AA9" s="74"/>
+      <c r="AB9" s="75"/>
       <c r="AC9" s="6"/>
       <c r="AD9" s="6"/>
       <c r="AE9" s="6"/>
-      <c r="AF9" s="75"/>
-      <c r="AG9" s="75"/>
-      <c r="AH9" s="75"/>
-      <c r="AI9" s="75"/>
-      <c r="AJ9" s="75"/>
-      <c r="AK9" s="75"/>
-      <c r="AL9" s="75"/>
-      <c r="AM9" s="75"/>
-      <c r="AN9" s="75"/>
-      <c r="AO9" s="75"/>
-      <c r="AP9" s="75"/>
+      <c r="AF9" s="82"/>
+      <c r="AG9" s="83"/>
+      <c r="AH9" s="83"/>
+      <c r="AI9" s="83"/>
+      <c r="AJ9" s="83"/>
+      <c r="AK9" s="83"/>
+      <c r="AL9" s="83"/>
+      <c r="AM9" s="83"/>
+      <c r="AN9" s="83"/>
+      <c r="AO9" s="83"/>
+      <c r="AP9" s="84"/>
       <c r="AQ9" s="1"/>
       <c r="AR9" s="1"/>
     </row>
-    <row r="10" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="72" t="s">
+    <row r="10" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="62">
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="66">
         <v>1</v>
       </c>
-      <c r="F10" s="62"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="58" t="s">
+      <c r="F10" s="66"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="59"/>
-      <c r="J10" s="43" t="s">
+      <c r="I10" s="63"/>
+      <c r="J10" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="60" t="s">
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="60"/>
-      <c r="O10" s="60"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="60"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="60"/>
-      <c r="U10" s="60"/>
-      <c r="V10" s="60"/>
-      <c r="W10" s="60"/>
-      <c r="X10" s="60"/>
-      <c r="Y10" s="60"/>
-      <c r="Z10" s="60"/>
-      <c r="AA10" s="60"/>
-      <c r="AB10" s="60"/>
-      <c r="AC10" s="43" t="s">
+      <c r="N10" s="64"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+      <c r="R10" s="64"/>
+      <c r="S10" s="64"/>
+      <c r="T10" s="64"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="64"/>
+      <c r="AA10" s="64"/>
+      <c r="AB10" s="64"/>
+      <c r="AC10" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="62">
+      <c r="AD10" s="53"/>
+      <c r="AE10" s="66">
         <v>114</v>
       </c>
-      <c r="AF10" s="63"/>
-      <c r="AG10" s="61" t="s">
+      <c r="AF10" s="67"/>
+      <c r="AG10" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="AH10" s="43" t="s">
+      <c r="AH10" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="AI10" s="43"/>
-      <c r="AJ10" s="43"/>
-      <c r="AK10" s="43"/>
-      <c r="AL10" s="56">
+      <c r="AI10" s="53"/>
+      <c r="AJ10" s="53"/>
+      <c r="AK10" s="53"/>
+      <c r="AL10" s="60">
         <v>0</v>
       </c>
-      <c r="AM10" s="56"/>
-      <c r="AN10" s="57"/>
-      <c r="AO10" s="58" t="s">
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="61"/>
+      <c r="AO10" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="AP10" s="59"/>
+      <c r="AP10" s="63"/>
       <c r="AQ10" s="1"/>
       <c r="AR10" s="1"/>
     </row>
-    <row r="11" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="72"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="60"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="60"/>
-      <c r="U11" s="60"/>
-      <c r="V11" s="60"/>
-      <c r="W11" s="60"/>
-      <c r="X11" s="60"/>
-      <c r="Y11" s="60"/>
-      <c r="Z11" s="60"/>
-      <c r="AA11" s="60"/>
-      <c r="AB11" s="60"/>
-      <c r="AC11" s="43"/>
-      <c r="AD11" s="43"/>
-      <c r="AE11" s="62"/>
-      <c r="AF11" s="63"/>
-      <c r="AG11" s="61"/>
-      <c r="AH11" s="43"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
-      <c r="AL11" s="56"/>
-      <c r="AM11" s="56"/>
-      <c r="AN11" s="57"/>
-      <c r="AO11" s="58"/>
-      <c r="AP11" s="59"/>
+    <row r="11" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="76"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="64"/>
+      <c r="R11" s="64"/>
+      <c r="S11" s="64"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="64"/>
+      <c r="AA11" s="64"/>
+      <c r="AB11" s="64"/>
+      <c r="AC11" s="53"/>
+      <c r="AD11" s="53"/>
+      <c r="AE11" s="66"/>
+      <c r="AF11" s="67"/>
+      <c r="AG11" s="65"/>
+      <c r="AH11" s="53"/>
+      <c r="AI11" s="53"/>
+      <c r="AJ11" s="53"/>
+      <c r="AK11" s="53"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="61"/>
+      <c r="AO11" s="62"/>
+      <c r="AP11" s="63"/>
       <c r="AQ11" s="1"/>
       <c r="AR11" s="1"/>
     </row>
-    <row r="12" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="30" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32"/>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="45"/>
-      <c r="W12" s="45"/>
-      <c r="X12" s="45"/>
-      <c r="Y12" s="45"/>
-      <c r="Z12" s="45"/>
-      <c r="AA12" s="45"/>
-      <c r="AB12" s="45"/>
-      <c r="AC12" s="45"/>
-      <c r="AD12" s="45"/>
-      <c r="AE12" s="45"/>
-      <c r="AF12" s="45"/>
-      <c r="AG12" s="45"/>
-      <c r="AH12" s="45"/>
-      <c r="AI12" s="45"/>
-      <c r="AJ12" s="45"/>
-      <c r="AK12" s="45"/>
-      <c r="AL12" s="45"/>
-      <c r="AM12" s="45"/>
-      <c r="AN12" s="45"/>
-      <c r="AO12" s="45"/>
-      <c r="AP12" s="46"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="55"/>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="55"/>
+      <c r="T12" s="55"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="55"/>
+      <c r="X12" s="55"/>
+      <c r="Y12" s="55"/>
+      <c r="Z12" s="55"/>
+      <c r="AA12" s="55"/>
+      <c r="AB12" s="55"/>
+      <c r="AC12" s="55"/>
+      <c r="AD12" s="55"/>
+      <c r="AE12" s="55"/>
+      <c r="AF12" s="55"/>
+      <c r="AG12" s="55"/>
+      <c r="AH12" s="55"/>
+      <c r="AI12" s="55"/>
+      <c r="AJ12" s="55"/>
+      <c r="AK12" s="55"/>
+      <c r="AL12" s="55"/>
+      <c r="AM12" s="55"/>
+      <c r="AN12" s="55"/>
+      <c r="AO12" s="55"/>
+      <c r="AP12" s="56"/>
       <c r="AQ12" s="1"/>
       <c r="AR12" s="1"/>
     </row>
-    <row r="13" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="65"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48"/>
-      <c r="V13" s="48"/>
-      <c r="W13" s="48"/>
-      <c r="X13" s="48"/>
-      <c r="Y13" s="48"/>
-      <c r="Z13" s="48"/>
-      <c r="AA13" s="48"/>
-      <c r="AB13" s="48"/>
-      <c r="AC13" s="48"/>
-      <c r="AD13" s="48"/>
-      <c r="AE13" s="48"/>
-      <c r="AF13" s="48"/>
-      <c r="AG13" s="48"/>
-      <c r="AH13" s="48"/>
-      <c r="AI13" s="48"/>
-      <c r="AJ13" s="48"/>
-      <c r="AK13" s="48"/>
-      <c r="AL13" s="48"/>
-      <c r="AM13" s="48"/>
-      <c r="AN13" s="48"/>
-      <c r="AO13" s="48"/>
-      <c r="AP13" s="49"/>
+    <row r="13" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="69"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="58"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="58"/>
+      <c r="S13" s="58"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="58"/>
+      <c r="V13" s="58"/>
+      <c r="W13" s="58"/>
+      <c r="X13" s="58"/>
+      <c r="Y13" s="58"/>
+      <c r="Z13" s="58"/>
+      <c r="AA13" s="58"/>
+      <c r="AB13" s="58"/>
+      <c r="AC13" s="58"/>
+      <c r="AD13" s="58"/>
+      <c r="AE13" s="58"/>
+      <c r="AF13" s="58"/>
+      <c r="AG13" s="58"/>
+      <c r="AH13" s="58"/>
+      <c r="AI13" s="58"/>
+      <c r="AJ13" s="58"/>
+      <c r="AK13" s="58"/>
+      <c r="AL13" s="58"/>
+      <c r="AM13" s="58"/>
+      <c r="AN13" s="58"/>
+      <c r="AO13" s="58"/>
+      <c r="AP13" s="59"/>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
     </row>
-    <row r="14" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="65"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
-      <c r="S14" s="36"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="36"/>
-      <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="36"/>
-      <c r="Y14" s="36"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="36"/>
-      <c r="AB14" s="36"/>
-      <c r="AC14" s="36"/>
-      <c r="AD14" s="36"/>
-      <c r="AE14" s="36"/>
-      <c r="AF14" s="36"/>
-      <c r="AG14" s="36"/>
-      <c r="AH14" s="36"/>
-      <c r="AI14" s="36"/>
-      <c r="AJ14" s="36"/>
-      <c r="AK14" s="36"/>
-      <c r="AL14" s="36"/>
-      <c r="AM14" s="36"/>
-      <c r="AN14" s="36"/>
-      <c r="AO14" s="36"/>
-      <c r="AP14" s="37"/>
+    <row r="14" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="69"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="108"/>
+      <c r="P14" s="108"/>
+      <c r="Q14" s="108"/>
+      <c r="R14" s="108"/>
+      <c r="S14" s="108"/>
+      <c r="T14" s="108"/>
+      <c r="U14" s="108"/>
+      <c r="V14" s="108"/>
+      <c r="W14" s="108"/>
+      <c r="X14" s="108"/>
+      <c r="Y14" s="108"/>
+      <c r="Z14" s="108"/>
+      <c r="AA14" s="108"/>
+      <c r="AB14" s="108"/>
+      <c r="AC14" s="108"/>
+      <c r="AD14" s="108"/>
+      <c r="AE14" s="108"/>
+      <c r="AF14" s="108"/>
+      <c r="AG14" s="108"/>
+      <c r="AH14" s="108"/>
+      <c r="AI14" s="108"/>
+      <c r="AJ14" s="108"/>
+      <c r="AK14" s="108"/>
+      <c r="AL14" s="108"/>
+      <c r="AM14" s="108"/>
+      <c r="AN14" s="108"/>
+      <c r="AO14" s="108"/>
+      <c r="AP14" s="109"/>
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
     </row>
-    <row r="15" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="33"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
       <c r="D15" s="35"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="38"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="38"/>
-      <c r="Y15" s="38"/>
-      <c r="Z15" s="38"/>
-      <c r="AA15" s="38"/>
-      <c r="AB15" s="38"/>
-      <c r="AC15" s="38"/>
-      <c r="AD15" s="38"/>
-      <c r="AE15" s="38"/>
-      <c r="AF15" s="38"/>
-      <c r="AG15" s="38"/>
-      <c r="AH15" s="38"/>
-      <c r="AI15" s="38"/>
-      <c r="AJ15" s="38"/>
-      <c r="AK15" s="38"/>
-      <c r="AL15" s="38"/>
-      <c r="AM15" s="38"/>
-      <c r="AN15" s="38"/>
-      <c r="AO15" s="38"/>
-      <c r="AP15" s="39"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="111"/>
+      <c r="S15" s="111"/>
+      <c r="T15" s="111"/>
+      <c r="U15" s="111"/>
+      <c r="V15" s="111"/>
+      <c r="W15" s="111"/>
+      <c r="X15" s="111"/>
+      <c r="Y15" s="111"/>
+      <c r="Z15" s="111"/>
+      <c r="AA15" s="111"/>
+      <c r="AB15" s="111"/>
+      <c r="AC15" s="111"/>
+      <c r="AD15" s="111"/>
+      <c r="AE15" s="111"/>
+      <c r="AF15" s="111"/>
+      <c r="AG15" s="111"/>
+      <c r="AH15" s="111"/>
+      <c r="AI15" s="111"/>
+      <c r="AJ15" s="111"/>
+      <c r="AK15" s="111"/>
+      <c r="AL15" s="111"/>
+      <c r="AM15" s="111"/>
+      <c r="AN15" s="111"/>
+      <c r="AO15" s="111"/>
+      <c r="AP15" s="112"/>
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
     </row>
-    <row r="16" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:44" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="18" t="s">
         <v>31</v>
       </c>
@@ -3249,31 +2154,31 @@
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
       <c r="U16" s="36"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="36"/>
-      <c r="AA16" s="36"/>
-      <c r="AB16" s="36"/>
-      <c r="AC16" s="36"/>
-      <c r="AD16" s="36"/>
-      <c r="AE16" s="36"/>
-      <c r="AF16" s="36"/>
-      <c r="AG16" s="36"/>
-      <c r="AH16" s="36"/>
-      <c r="AI16" s="36"/>
-      <c r="AJ16" s="36"/>
-      <c r="AK16" s="36"/>
-      <c r="AL16" s="36"/>
-      <c r="AM16" s="36"/>
-      <c r="AN16" s="36"/>
-      <c r="AO16" s="36"/>
-      <c r="AP16" s="37"/>
+      <c r="V16" s="37"/>
+      <c r="W16" s="37"/>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="37"/>
+      <c r="Z16" s="37"/>
+      <c r="AA16" s="37"/>
+      <c r="AB16" s="37"/>
+      <c r="AC16" s="37"/>
+      <c r="AD16" s="37"/>
+      <c r="AE16" s="37"/>
+      <c r="AF16" s="37"/>
+      <c r="AG16" s="37"/>
+      <c r="AH16" s="37"/>
+      <c r="AI16" s="37"/>
+      <c r="AJ16" s="37"/>
+      <c r="AK16" s="37"/>
+      <c r="AL16" s="37"/>
+      <c r="AM16" s="37"/>
+      <c r="AN16" s="37"/>
+      <c r="AO16" s="37"/>
+      <c r="AP16" s="38"/>
       <c r="AQ16" s="1"/>
       <c r="AR16" s="1"/>
     </row>
-    <row r="17" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="21"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -3294,32 +2199,32 @@
       <c r="R17" s="34"/>
       <c r="S17" s="34"/>
       <c r="T17" s="35"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="38"/>
-      <c r="Y17" s="38"/>
-      <c r="Z17" s="38"/>
-      <c r="AA17" s="38"/>
-      <c r="AB17" s="38"/>
-      <c r="AC17" s="38"/>
-      <c r="AD17" s="38"/>
-      <c r="AE17" s="38"/>
-      <c r="AF17" s="38"/>
-      <c r="AG17" s="38"/>
-      <c r="AH17" s="38"/>
-      <c r="AI17" s="38"/>
-      <c r="AJ17" s="38"/>
-      <c r="AK17" s="38"/>
-      <c r="AL17" s="38"/>
-      <c r="AM17" s="38"/>
-      <c r="AN17" s="38"/>
-      <c r="AO17" s="38"/>
-      <c r="AP17" s="39"/>
+      <c r="U17" s="39"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="40"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="40"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="40"/>
+      <c r="AC17" s="40"/>
+      <c r="AD17" s="40"/>
+      <c r="AE17" s="40"/>
+      <c r="AF17" s="40"/>
+      <c r="AG17" s="40"/>
+      <c r="AH17" s="40"/>
+      <c r="AI17" s="40"/>
+      <c r="AJ17" s="40"/>
+      <c r="AK17" s="40"/>
+      <c r="AL17" s="40"/>
+      <c r="AM17" s="40"/>
+      <c r="AN17" s="40"/>
+      <c r="AO17" s="40"/>
+      <c r="AP17" s="41"/>
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
     </row>
-    <row r="18" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="s">
         <v>20</v>
       </c>
@@ -3330,7 +2235,7 @@
         <v>21</v>
       </c>
       <c r="F18" s="7"/>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="68" t="s">
         <v>40</v>
       </c>
       <c r="H18" s="8"/>
@@ -3355,25 +2260,25 @@
       </c>
       <c r="Z18" s="7"/>
       <c r="AA18" s="7"/>
-      <c r="AB18" s="42"/>
-      <c r="AC18" s="42"/>
-      <c r="AD18" s="42"/>
-      <c r="AE18" s="42"/>
-      <c r="AF18" s="42"/>
-      <c r="AG18" s="42"/>
-      <c r="AH18" s="42"/>
-      <c r="AI18" s="42"/>
-      <c r="AJ18" s="42"/>
-      <c r="AK18" s="42"/>
-      <c r="AL18" s="42"/>
-      <c r="AM18" s="42"/>
-      <c r="AN18" s="42"/>
-      <c r="AO18" s="42"/>
-      <c r="AP18" s="42"/>
+      <c r="AB18" s="52"/>
+      <c r="AC18" s="52"/>
+      <c r="AD18" s="52"/>
+      <c r="AE18" s="52"/>
+      <c r="AF18" s="52"/>
+      <c r="AG18" s="52"/>
+      <c r="AH18" s="52"/>
+      <c r="AI18" s="52"/>
+      <c r="AJ18" s="52"/>
+      <c r="AK18" s="52"/>
+      <c r="AL18" s="52"/>
+      <c r="AM18" s="52"/>
+      <c r="AN18" s="52"/>
+      <c r="AO18" s="52"/>
+      <c r="AP18" s="52"/>
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
     </row>
-    <row r="19" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -3401,25 +2306,25 @@
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
       <c r="AA19" s="7"/>
-      <c r="AB19" s="42"/>
-      <c r="AC19" s="42"/>
-      <c r="AD19" s="42"/>
-      <c r="AE19" s="42"/>
-      <c r="AF19" s="42"/>
-      <c r="AG19" s="42"/>
-      <c r="AH19" s="42"/>
-      <c r="AI19" s="42"/>
-      <c r="AJ19" s="42"/>
-      <c r="AK19" s="42"/>
-      <c r="AL19" s="42"/>
-      <c r="AM19" s="42"/>
-      <c r="AN19" s="42"/>
-      <c r="AO19" s="42"/>
-      <c r="AP19" s="42"/>
+      <c r="AB19" s="52"/>
+      <c r="AC19" s="52"/>
+      <c r="AD19" s="52"/>
+      <c r="AE19" s="52"/>
+      <c r="AF19" s="52"/>
+      <c r="AG19" s="52"/>
+      <c r="AH19" s="52"/>
+      <c r="AI19" s="52"/>
+      <c r="AJ19" s="52"/>
+      <c r="AK19" s="52"/>
+      <c r="AL19" s="52"/>
+      <c r="AM19" s="52"/>
+      <c r="AN19" s="52"/>
+      <c r="AO19" s="52"/>
+      <c r="AP19" s="52"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
     </row>
-    <row r="20" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -3451,25 +2356,25 @@
       </c>
       <c r="Z20" s="7"/>
       <c r="AA20" s="7"/>
-      <c r="AB20" s="41"/>
-      <c r="AC20" s="41"/>
-      <c r="AD20" s="41"/>
-      <c r="AE20" s="41"/>
-      <c r="AF20" s="41"/>
-      <c r="AG20" s="41"/>
-      <c r="AH20" s="41"/>
-      <c r="AI20" s="41"/>
-      <c r="AJ20" s="41"/>
-      <c r="AK20" s="41"/>
-      <c r="AL20" s="41"/>
-      <c r="AM20" s="41"/>
-      <c r="AN20" s="41"/>
-      <c r="AO20" s="41"/>
-      <c r="AP20" s="41"/>
+      <c r="AB20" s="51"/>
+      <c r="AC20" s="51"/>
+      <c r="AD20" s="51"/>
+      <c r="AE20" s="51"/>
+      <c r="AF20" s="51"/>
+      <c r="AG20" s="51"/>
+      <c r="AH20" s="51"/>
+      <c r="AI20" s="51"/>
+      <c r="AJ20" s="51"/>
+      <c r="AK20" s="51"/>
+      <c r="AL20" s="51"/>
+      <c r="AM20" s="51"/>
+      <c r="AN20" s="51"/>
+      <c r="AO20" s="51"/>
+      <c r="AP20" s="51"/>
       <c r="AQ20" s="1"/>
       <c r="AR20" s="1"/>
     </row>
-    <row r="21" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3497,25 +2402,25 @@
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
-      <c r="AB21" s="41"/>
-      <c r="AC21" s="41"/>
-      <c r="AD21" s="41"/>
-      <c r="AE21" s="41"/>
-      <c r="AF21" s="41"/>
-      <c r="AG21" s="41"/>
-      <c r="AH21" s="41"/>
-      <c r="AI21" s="41"/>
-      <c r="AJ21" s="41"/>
-      <c r="AK21" s="41"/>
-      <c r="AL21" s="41"/>
-      <c r="AM21" s="41"/>
-      <c r="AN21" s="41"/>
-      <c r="AO21" s="41"/>
-      <c r="AP21" s="41"/>
+      <c r="AB21" s="51"/>
+      <c r="AC21" s="51"/>
+      <c r="AD21" s="51"/>
+      <c r="AE21" s="51"/>
+      <c r="AF21" s="51"/>
+      <c r="AG21" s="51"/>
+      <c r="AH21" s="51"/>
+      <c r="AI21" s="51"/>
+      <c r="AJ21" s="51"/>
+      <c r="AK21" s="51"/>
+      <c r="AL21" s="51"/>
+      <c r="AM21" s="51"/>
+      <c r="AN21" s="51"/>
+      <c r="AO21" s="51"/>
+      <c r="AP21" s="51"/>
       <c r="AQ21" s="1"/>
       <c r="AR21" s="1"/>
     </row>
-    <row r="22" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -3547,25 +2452,25 @@
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
-      <c r="AB22" s="41"/>
-      <c r="AC22" s="41"/>
-      <c r="AD22" s="41"/>
-      <c r="AE22" s="41"/>
-      <c r="AF22" s="41"/>
-      <c r="AG22" s="41"/>
-      <c r="AH22" s="41"/>
-      <c r="AI22" s="41"/>
-      <c r="AJ22" s="41"/>
-      <c r="AK22" s="41"/>
-      <c r="AL22" s="41"/>
-      <c r="AM22" s="41"/>
-      <c r="AN22" s="41"/>
-      <c r="AO22" s="41"/>
-      <c r="AP22" s="41"/>
+      <c r="AB22" s="51"/>
+      <c r="AC22" s="51"/>
+      <c r="AD22" s="51"/>
+      <c r="AE22" s="51"/>
+      <c r="AF22" s="51"/>
+      <c r="AG22" s="51"/>
+      <c r="AH22" s="51"/>
+      <c r="AI22" s="51"/>
+      <c r="AJ22" s="51"/>
+      <c r="AK22" s="51"/>
+      <c r="AL22" s="51"/>
+      <c r="AM22" s="51"/>
+      <c r="AN22" s="51"/>
+      <c r="AO22" s="51"/>
+      <c r="AP22" s="51"/>
       <c r="AQ22" s="1"/>
       <c r="AR22" s="1"/>
     </row>
-    <row r="23" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -3593,25 +2498,25 @@
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
       <c r="AA23" s="7"/>
-      <c r="AB23" s="41"/>
-      <c r="AC23" s="41"/>
-      <c r="AD23" s="41"/>
-      <c r="AE23" s="41"/>
-      <c r="AF23" s="41"/>
-      <c r="AG23" s="41"/>
-      <c r="AH23" s="41"/>
-      <c r="AI23" s="41"/>
-      <c r="AJ23" s="41"/>
-      <c r="AK23" s="41"/>
-      <c r="AL23" s="41"/>
-      <c r="AM23" s="41"/>
-      <c r="AN23" s="41"/>
-      <c r="AO23" s="41"/>
-      <c r="AP23" s="41"/>
+      <c r="AB23" s="51"/>
+      <c r="AC23" s="51"/>
+      <c r="AD23" s="51"/>
+      <c r="AE23" s="51"/>
+      <c r="AF23" s="51"/>
+      <c r="AG23" s="51"/>
+      <c r="AH23" s="51"/>
+      <c r="AI23" s="51"/>
+      <c r="AJ23" s="51"/>
+      <c r="AK23" s="51"/>
+      <c r="AL23" s="51"/>
+      <c r="AM23" s="51"/>
+      <c r="AN23" s="51"/>
+      <c r="AO23" s="51"/>
+      <c r="AP23" s="51"/>
       <c r="AQ23" s="1"/>
       <c r="AR23" s="1"/>
     </row>
-    <row r="24" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -3643,25 +2548,25 @@
       </c>
       <c r="Z24" s="7"/>
       <c r="AA24" s="7"/>
-      <c r="AB24" s="41"/>
-      <c r="AC24" s="41"/>
-      <c r="AD24" s="41"/>
-      <c r="AE24" s="41"/>
-      <c r="AF24" s="41"/>
-      <c r="AG24" s="41"/>
-      <c r="AH24" s="41"/>
-      <c r="AI24" s="41"/>
-      <c r="AJ24" s="41"/>
-      <c r="AK24" s="41"/>
-      <c r="AL24" s="41"/>
-      <c r="AM24" s="41"/>
-      <c r="AN24" s="41"/>
-      <c r="AO24" s="41"/>
-      <c r="AP24" s="41"/>
+      <c r="AB24" s="51"/>
+      <c r="AC24" s="51"/>
+      <c r="AD24" s="51"/>
+      <c r="AE24" s="51"/>
+      <c r="AF24" s="51"/>
+      <c r="AG24" s="51"/>
+      <c r="AH24" s="51"/>
+      <c r="AI24" s="51"/>
+      <c r="AJ24" s="51"/>
+      <c r="AK24" s="51"/>
+      <c r="AL24" s="51"/>
+      <c r="AM24" s="51"/>
+      <c r="AN24" s="51"/>
+      <c r="AO24" s="51"/>
+      <c r="AP24" s="51"/>
       <c r="AQ24" s="1"/>
       <c r="AR24" s="1"/>
     </row>
-    <row r="25" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -3689,25 +2594,25 @@
       <c r="Y25" s="7"/>
       <c r="Z25" s="7"/>
       <c r="AA25" s="7"/>
-      <c r="AB25" s="41"/>
-      <c r="AC25" s="41"/>
-      <c r="AD25" s="41"/>
-      <c r="AE25" s="41"/>
-      <c r="AF25" s="41"/>
-      <c r="AG25" s="41"/>
-      <c r="AH25" s="41"/>
-      <c r="AI25" s="41"/>
-      <c r="AJ25" s="41"/>
-      <c r="AK25" s="41"/>
-      <c r="AL25" s="41"/>
-      <c r="AM25" s="41"/>
-      <c r="AN25" s="41"/>
-      <c r="AO25" s="41"/>
-      <c r="AP25" s="41"/>
+      <c r="AB25" s="51"/>
+      <c r="AC25" s="51"/>
+      <c r="AD25" s="51"/>
+      <c r="AE25" s="51"/>
+      <c r="AF25" s="51"/>
+      <c r="AG25" s="51"/>
+      <c r="AH25" s="51"/>
+      <c r="AI25" s="51"/>
+      <c r="AJ25" s="51"/>
+      <c r="AK25" s="51"/>
+      <c r="AL25" s="51"/>
+      <c r="AM25" s="51"/>
+      <c r="AN25" s="51"/>
+      <c r="AO25" s="51"/>
+      <c r="AP25" s="51"/>
       <c r="AQ25" s="1"/>
       <c r="AR25" s="1"/>
     </row>
-    <row r="26" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
         <v>25</v>
       </c>
@@ -3743,25 +2648,25 @@
       </c>
       <c r="Z26" s="7"/>
       <c r="AA26" s="7"/>
-      <c r="AB26" s="41"/>
-      <c r="AC26" s="41"/>
-      <c r="AD26" s="41"/>
-      <c r="AE26" s="41"/>
-      <c r="AF26" s="41"/>
-      <c r="AG26" s="41"/>
-      <c r="AH26" s="41"/>
-      <c r="AI26" s="41"/>
-      <c r="AJ26" s="41"/>
-      <c r="AK26" s="41"/>
-      <c r="AL26" s="41"/>
-      <c r="AM26" s="41"/>
-      <c r="AN26" s="41"/>
-      <c r="AO26" s="41"/>
-      <c r="AP26" s="41"/>
+      <c r="AB26" s="51"/>
+      <c r="AC26" s="51"/>
+      <c r="AD26" s="51"/>
+      <c r="AE26" s="51"/>
+      <c r="AF26" s="51"/>
+      <c r="AG26" s="51"/>
+      <c r="AH26" s="51"/>
+      <c r="AI26" s="51"/>
+      <c r="AJ26" s="51"/>
+      <c r="AK26" s="51"/>
+      <c r="AL26" s="51"/>
+      <c r="AM26" s="51"/>
+      <c r="AN26" s="51"/>
+      <c r="AO26" s="51"/>
+      <c r="AP26" s="51"/>
       <c r="AQ26" s="1"/>
       <c r="AR26" s="1"/>
     </row>
-    <row r="27" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -3789,25 +2694,25 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
       <c r="AA27" s="7"/>
-      <c r="AB27" s="41"/>
-      <c r="AC27" s="41"/>
-      <c r="AD27" s="41"/>
-      <c r="AE27" s="41"/>
-      <c r="AF27" s="41"/>
-      <c r="AG27" s="41"/>
-      <c r="AH27" s="41"/>
-      <c r="AI27" s="41"/>
-      <c r="AJ27" s="41"/>
-      <c r="AK27" s="41"/>
-      <c r="AL27" s="41"/>
-      <c r="AM27" s="41"/>
-      <c r="AN27" s="41"/>
-      <c r="AO27" s="41"/>
-      <c r="AP27" s="41"/>
+      <c r="AB27" s="51"/>
+      <c r="AC27" s="51"/>
+      <c r="AD27" s="51"/>
+      <c r="AE27" s="51"/>
+      <c r="AF27" s="51"/>
+      <c r="AG27" s="51"/>
+      <c r="AH27" s="51"/>
+      <c r="AI27" s="51"/>
+      <c r="AJ27" s="51"/>
+      <c r="AK27" s="51"/>
+      <c r="AL27" s="51"/>
+      <c r="AM27" s="51"/>
+      <c r="AN27" s="51"/>
+      <c r="AO27" s="51"/>
+      <c r="AP27" s="51"/>
       <c r="AQ27" s="1"/>
       <c r="AR27" s="1"/>
     </row>
-    <row r="28" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -3839,25 +2744,25 @@
       </c>
       <c r="Z28" s="7"/>
       <c r="AA28" s="7"/>
-      <c r="AB28" s="41"/>
-      <c r="AC28" s="41"/>
-      <c r="AD28" s="41"/>
-      <c r="AE28" s="41"/>
-      <c r="AF28" s="41"/>
-      <c r="AG28" s="41"/>
-      <c r="AH28" s="41"/>
-      <c r="AI28" s="41"/>
-      <c r="AJ28" s="41"/>
-      <c r="AK28" s="41"/>
-      <c r="AL28" s="41"/>
-      <c r="AM28" s="41"/>
-      <c r="AN28" s="41"/>
-      <c r="AO28" s="41"/>
-      <c r="AP28" s="41"/>
+      <c r="AB28" s="51"/>
+      <c r="AC28" s="51"/>
+      <c r="AD28" s="51"/>
+      <c r="AE28" s="51"/>
+      <c r="AF28" s="51"/>
+      <c r="AG28" s="51"/>
+      <c r="AH28" s="51"/>
+      <c r="AI28" s="51"/>
+      <c r="AJ28" s="51"/>
+      <c r="AK28" s="51"/>
+      <c r="AL28" s="51"/>
+      <c r="AM28" s="51"/>
+      <c r="AN28" s="51"/>
+      <c r="AO28" s="51"/>
+      <c r="AP28" s="51"/>
       <c r="AQ28" s="1"/>
       <c r="AR28" s="1"/>
     </row>
-    <row r="29" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -3885,25 +2790,25 @@
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
-      <c r="AB29" s="41"/>
-      <c r="AC29" s="41"/>
-      <c r="AD29" s="41"/>
-      <c r="AE29" s="41"/>
-      <c r="AF29" s="41"/>
-      <c r="AG29" s="41"/>
-      <c r="AH29" s="41"/>
-      <c r="AI29" s="41"/>
-      <c r="AJ29" s="41"/>
-      <c r="AK29" s="41"/>
-      <c r="AL29" s="41"/>
-      <c r="AM29" s="41"/>
-      <c r="AN29" s="41"/>
-      <c r="AO29" s="41"/>
-      <c r="AP29" s="41"/>
+      <c r="AB29" s="51"/>
+      <c r="AC29" s="51"/>
+      <c r="AD29" s="51"/>
+      <c r="AE29" s="51"/>
+      <c r="AF29" s="51"/>
+      <c r="AG29" s="51"/>
+      <c r="AH29" s="51"/>
+      <c r="AI29" s="51"/>
+      <c r="AJ29" s="51"/>
+      <c r="AK29" s="51"/>
+      <c r="AL29" s="51"/>
+      <c r="AM29" s="51"/>
+      <c r="AN29" s="51"/>
+      <c r="AO29" s="51"/>
+      <c r="AP29" s="51"/>
       <c r="AQ29" s="1"/>
       <c r="AR29" s="1"/>
     </row>
-    <row r="30" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -3935,25 +2840,25 @@
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
-      <c r="AB30" s="41"/>
-      <c r="AC30" s="41"/>
-      <c r="AD30" s="41"/>
-      <c r="AE30" s="41"/>
-      <c r="AF30" s="41"/>
-      <c r="AG30" s="41"/>
-      <c r="AH30" s="41"/>
-      <c r="AI30" s="41"/>
-      <c r="AJ30" s="41"/>
-      <c r="AK30" s="41"/>
-      <c r="AL30" s="41"/>
-      <c r="AM30" s="41"/>
-      <c r="AN30" s="41"/>
-      <c r="AO30" s="41"/>
-      <c r="AP30" s="41"/>
+      <c r="AB30" s="51"/>
+      <c r="AC30" s="51"/>
+      <c r="AD30" s="51"/>
+      <c r="AE30" s="51"/>
+      <c r="AF30" s="51"/>
+      <c r="AG30" s="51"/>
+      <c r="AH30" s="51"/>
+      <c r="AI30" s="51"/>
+      <c r="AJ30" s="51"/>
+      <c r="AK30" s="51"/>
+      <c r="AL30" s="51"/>
+      <c r="AM30" s="51"/>
+      <c r="AN30" s="51"/>
+      <c r="AO30" s="51"/>
+      <c r="AP30" s="51"/>
       <c r="AQ30" s="1"/>
       <c r="AR30" s="1"/>
     </row>
-    <row r="31" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -3981,26 +2886,26 @@
       <c r="Y31" s="7"/>
       <c r="Z31" s="7"/>
       <c r="AA31" s="7"/>
-      <c r="AB31" s="41"/>
-      <c r="AC31" s="41"/>
-      <c r="AD31" s="41"/>
-      <c r="AE31" s="41"/>
-      <c r="AF31" s="41"/>
-      <c r="AG31" s="41"/>
-      <c r="AH31" s="41"/>
-      <c r="AI31" s="41"/>
-      <c r="AJ31" s="41"/>
-      <c r="AK31" s="41"/>
-      <c r="AL31" s="41"/>
-      <c r="AM31" s="41"/>
-      <c r="AN31" s="41"/>
-      <c r="AO31" s="41"/>
-      <c r="AP31" s="41"/>
+      <c r="AB31" s="51"/>
+      <c r="AC31" s="51"/>
+      <c r="AD31" s="51"/>
+      <c r="AE31" s="51"/>
+      <c r="AF31" s="51"/>
+      <c r="AG31" s="51"/>
+      <c r="AH31" s="51"/>
+      <c r="AI31" s="51"/>
+      <c r="AJ31" s="51"/>
+      <c r="AK31" s="51"/>
+      <c r="AL31" s="51"/>
+      <c r="AM31" s="51"/>
+      <c r="AN31" s="51"/>
+      <c r="AO31" s="51"/>
+      <c r="AP31" s="51"/>
       <c r="AQ31" s="1"/>
       <c r="AR31" s="1"/>
       <c r="AU31" s="5"/>
     </row>
-    <row r="32" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -4032,26 +2937,26 @@
       </c>
       <c r="Z32" s="7"/>
       <c r="AA32" s="7"/>
-      <c r="AB32" s="41"/>
-      <c r="AC32" s="41"/>
-      <c r="AD32" s="41"/>
-      <c r="AE32" s="41"/>
-      <c r="AF32" s="41"/>
-      <c r="AG32" s="41"/>
-      <c r="AH32" s="41"/>
-      <c r="AI32" s="41"/>
-      <c r="AJ32" s="41"/>
-      <c r="AK32" s="41"/>
-      <c r="AL32" s="41"/>
-      <c r="AM32" s="41"/>
-      <c r="AN32" s="41"/>
-      <c r="AO32" s="41"/>
-      <c r="AP32" s="41"/>
+      <c r="AB32" s="51"/>
+      <c r="AC32" s="51"/>
+      <c r="AD32" s="51"/>
+      <c r="AE32" s="51"/>
+      <c r="AF32" s="51"/>
+      <c r="AG32" s="51"/>
+      <c r="AH32" s="51"/>
+      <c r="AI32" s="51"/>
+      <c r="AJ32" s="51"/>
+      <c r="AK32" s="51"/>
+      <c r="AL32" s="51"/>
+      <c r="AM32" s="51"/>
+      <c r="AN32" s="51"/>
+      <c r="AO32" s="51"/>
+      <c r="AP32" s="51"/>
       <c r="AQ32" s="1"/>
       <c r="AR32" s="1"/>
       <c r="AU32" s="5"/>
     </row>
-    <row r="33" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -4079,26 +2984,26 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
       <c r="AA33" s="7"/>
-      <c r="AB33" s="41"/>
-      <c r="AC33" s="41"/>
-      <c r="AD33" s="41"/>
-      <c r="AE33" s="41"/>
-      <c r="AF33" s="41"/>
-      <c r="AG33" s="41"/>
-      <c r="AH33" s="41"/>
-      <c r="AI33" s="41"/>
-      <c r="AJ33" s="41"/>
-      <c r="AK33" s="41"/>
-      <c r="AL33" s="41"/>
-      <c r="AM33" s="41"/>
-      <c r="AN33" s="41"/>
-      <c r="AO33" s="41"/>
-      <c r="AP33" s="41"/>
+      <c r="AB33" s="51"/>
+      <c r="AC33" s="51"/>
+      <c r="AD33" s="51"/>
+      <c r="AE33" s="51"/>
+      <c r="AF33" s="51"/>
+      <c r="AG33" s="51"/>
+      <c r="AH33" s="51"/>
+      <c r="AI33" s="51"/>
+      <c r="AJ33" s="51"/>
+      <c r="AK33" s="51"/>
+      <c r="AL33" s="51"/>
+      <c r="AM33" s="51"/>
+      <c r="AN33" s="51"/>
+      <c r="AO33" s="51"/>
+      <c r="AP33" s="51"/>
       <c r="AQ33" s="1"/>
       <c r="AR33" s="1"/>
       <c r="AU33" s="5"/>
     </row>
-    <row r="34" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="6" t="s">
         <v>27</v>
       </c>
@@ -4147,7 +3052,7 @@
       <c r="AR34" s="1"/>
       <c r="AU34" s="5"/>
     </row>
-    <row r="35" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -4194,7 +3099,7 @@
       <c r="AR35" s="1"/>
       <c r="AU35" s="5"/>
     </row>
-    <row r="36" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="9" t="s">
         <v>44</v>
       </c>
@@ -4242,7 +3147,7 @@
       <c r="AQ36" s="1"/>
       <c r="AR36" s="1"/>
     </row>
-    <row r="37" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="12"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -4288,7 +3193,7 @@
       <c r="AQ37" s="1"/>
       <c r="AR37" s="1"/>
     </row>
-    <row r="38" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="12"/>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -4334,7 +3239,7 @@
       <c r="AQ38" s="1"/>
       <c r="AR38" s="1"/>
     </row>
-    <row r="39" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="12"/>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -4380,7 +3285,7 @@
       <c r="AQ39" s="1"/>
       <c r="AR39" s="1"/>
     </row>
-    <row r="40" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="12"/>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
@@ -4426,7 +3331,7 @@
       <c r="AQ40" s="1"/>
       <c r="AR40" s="1"/>
     </row>
-    <row r="41" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="12"/>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -4472,7 +3377,7 @@
       <c r="AQ41" s="1"/>
       <c r="AR41" s="1"/>
     </row>
-    <row r="42" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="12"/>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -4518,7 +3423,7 @@
       <c r="AQ42" s="1"/>
       <c r="AR42" s="1"/>
     </row>
-    <row r="43" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="12"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4564,7 +3469,7 @@
       <c r="AQ43" s="1"/>
       <c r="AR43" s="1"/>
     </row>
-    <row r="44" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="12"/>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -4610,7 +3515,7 @@
       <c r="AQ44" s="1"/>
       <c r="AR44" s="1"/>
     </row>
-    <row r="45" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="12"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -4656,7 +3561,7 @@
       <c r="AQ45" s="1"/>
       <c r="AR45" s="1"/>
     </row>
-    <row r="46" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="12"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
@@ -4702,7 +3607,7 @@
       <c r="AQ46" s="1"/>
       <c r="AR46" s="1"/>
     </row>
-    <row r="47" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="12"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -4748,7 +3653,7 @@
       <c r="AQ47" s="1"/>
       <c r="AR47" s="1"/>
     </row>
-    <row r="48" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:47" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="12"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
@@ -4794,7 +3699,7 @@
       <c r="AQ48" s="1"/>
       <c r="AR48" s="1"/>
     </row>
-    <row r="49" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="12"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
@@ -4840,7 +3745,7 @@
       <c r="AQ49" s="1"/>
       <c r="AR49" s="1"/>
     </row>
-    <row r="50" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="12"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -4886,7 +3791,7 @@
       <c r="AQ50" s="1"/>
       <c r="AR50" s="1"/>
     </row>
-    <row r="51" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="15"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -4932,7 +3837,7 @@
       <c r="AQ51" s="1"/>
       <c r="AR51" s="1"/>
     </row>
-    <row r="52" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="6" t="s">
         <v>29</v>
       </c>
@@ -4980,7 +3885,7 @@
       <c r="AQ52" s="1"/>
       <c r="AR52" s="1"/>
     </row>
-    <row r="53" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -5026,331 +3931,331 @@
       <c r="AQ53" s="1"/>
       <c r="AR53" s="1"/>
     </row>
-    <row r="54" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="40" t="s">
+    <row r="54" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="40"/>
-      <c r="K54" s="40"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
-      <c r="N54" s="40"/>
-      <c r="O54" s="40"/>
-      <c r="P54" s="40"/>
-      <c r="Q54" s="40"/>
-      <c r="R54" s="40"/>
-      <c r="S54" s="40"/>
-      <c r="T54" s="40"/>
-      <c r="U54" s="40"/>
-      <c r="V54" s="40"/>
-      <c r="W54" s="40"/>
-      <c r="X54" s="40"/>
-      <c r="Y54" s="40"/>
-      <c r="Z54" s="40"/>
-      <c r="AA54" s="40"/>
-      <c r="AB54" s="40"/>
-      <c r="AC54" s="40"/>
-      <c r="AD54" s="40"/>
-      <c r="AE54" s="40"/>
-      <c r="AF54" s="40"/>
-      <c r="AG54" s="40"/>
-      <c r="AH54" s="40"/>
-      <c r="AI54" s="40"/>
-      <c r="AJ54" s="40"/>
-      <c r="AK54" s="40"/>
-      <c r="AL54" s="40"/>
-      <c r="AM54" s="40"/>
-      <c r="AN54" s="40"/>
-      <c r="AO54" s="40"/>
-      <c r="AP54" s="40"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+      <c r="L54" s="43"/>
+      <c r="M54" s="43"/>
+      <c r="N54" s="43"/>
+      <c r="O54" s="43"/>
+      <c r="P54" s="43"/>
+      <c r="Q54" s="43"/>
+      <c r="R54" s="43"/>
+      <c r="S54" s="43"/>
+      <c r="T54" s="43"/>
+      <c r="U54" s="43"/>
+      <c r="V54" s="43"/>
+      <c r="W54" s="43"/>
+      <c r="X54" s="43"/>
+      <c r="Y54" s="43"/>
+      <c r="Z54" s="43"/>
+      <c r="AA54" s="43"/>
+      <c r="AB54" s="43"/>
+      <c r="AC54" s="43"/>
+      <c r="AD54" s="43"/>
+      <c r="AE54" s="43"/>
+      <c r="AF54" s="43"/>
+      <c r="AG54" s="43"/>
+      <c r="AH54" s="43"/>
+      <c r="AI54" s="43"/>
+      <c r="AJ54" s="43"/>
+      <c r="AK54" s="43"/>
+      <c r="AL54" s="43"/>
+      <c r="AM54" s="43"/>
+      <c r="AN54" s="43"/>
+      <c r="AO54" s="43"/>
+      <c r="AP54" s="44"/>
       <c r="AQ54" s="1"/>
       <c r="AR54" s="1"/>
     </row>
-    <row r="55" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="40"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="40"/>
-      <c r="L55" s="40"/>
-      <c r="M55" s="40"/>
-      <c r="N55" s="40"/>
-      <c r="O55" s="40"/>
-      <c r="P55" s="40"/>
-      <c r="Q55" s="40"/>
-      <c r="R55" s="40"/>
-      <c r="S55" s="40"/>
-      <c r="T55" s="40"/>
-      <c r="U55" s="40"/>
-      <c r="V55" s="40"/>
-      <c r="W55" s="40"/>
-      <c r="X55" s="40"/>
-      <c r="Y55" s="40"/>
-      <c r="Z55" s="40"/>
-      <c r="AA55" s="40"/>
-      <c r="AB55" s="40"/>
-      <c r="AC55" s="40"/>
-      <c r="AD55" s="40"/>
-      <c r="AE55" s="40"/>
-      <c r="AF55" s="40"/>
-      <c r="AG55" s="40"/>
-      <c r="AH55" s="40"/>
-      <c r="AI55" s="40"/>
-      <c r="AJ55" s="40"/>
-      <c r="AK55" s="40"/>
-      <c r="AL55" s="40"/>
-      <c r="AM55" s="40"/>
-      <c r="AN55" s="40"/>
-      <c r="AO55" s="40"/>
-      <c r="AP55" s="40"/>
+    <row r="55" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="45"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
+      <c r="L55" s="46"/>
+      <c r="M55" s="46"/>
+      <c r="N55" s="46"/>
+      <c r="O55" s="46"/>
+      <c r="P55" s="46"/>
+      <c r="Q55" s="46"/>
+      <c r="R55" s="46"/>
+      <c r="S55" s="46"/>
+      <c r="T55" s="46"/>
+      <c r="U55" s="46"/>
+      <c r="V55" s="46"/>
+      <c r="W55" s="46"/>
+      <c r="X55" s="46"/>
+      <c r="Y55" s="46"/>
+      <c r="Z55" s="46"/>
+      <c r="AA55" s="46"/>
+      <c r="AB55" s="46"/>
+      <c r="AC55" s="46"/>
+      <c r="AD55" s="46"/>
+      <c r="AE55" s="46"/>
+      <c r="AF55" s="46"/>
+      <c r="AG55" s="46"/>
+      <c r="AH55" s="46"/>
+      <c r="AI55" s="46"/>
+      <c r="AJ55" s="46"/>
+      <c r="AK55" s="46"/>
+      <c r="AL55" s="46"/>
+      <c r="AM55" s="46"/>
+      <c r="AN55" s="46"/>
+      <c r="AO55" s="46"/>
+      <c r="AP55" s="47"/>
       <c r="AQ55" s="1"/>
       <c r="AR55" s="1"/>
     </row>
-    <row r="56" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="40"/>
-      <c r="B56" s="40"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="40"/>
-      <c r="K56" s="40"/>
-      <c r="L56" s="40"/>
-      <c r="M56" s="40"/>
-      <c r="N56" s="40"/>
-      <c r="O56" s="40"/>
-      <c r="P56" s="40"/>
-      <c r="Q56" s="40"/>
-      <c r="R56" s="40"/>
-      <c r="S56" s="40"/>
-      <c r="T56" s="40"/>
-      <c r="U56" s="40"/>
-      <c r="V56" s="40"/>
-      <c r="W56" s="40"/>
-      <c r="X56" s="40"/>
-      <c r="Y56" s="40"/>
-      <c r="Z56" s="40"/>
-      <c r="AA56" s="40"/>
-      <c r="AB56" s="40"/>
-      <c r="AC56" s="40"/>
-      <c r="AD56" s="40"/>
-      <c r="AE56" s="40"/>
-      <c r="AF56" s="40"/>
-      <c r="AG56" s="40"/>
-      <c r="AH56" s="40"/>
-      <c r="AI56" s="40"/>
-      <c r="AJ56" s="40"/>
-      <c r="AK56" s="40"/>
-      <c r="AL56" s="40"/>
-      <c r="AM56" s="40"/>
-      <c r="AN56" s="40"/>
-      <c r="AO56" s="40"/>
-      <c r="AP56" s="40"/>
+    <row r="56" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="45"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="46"/>
+      <c r="I56" s="46"/>
+      <c r="J56" s="46"/>
+      <c r="K56" s="46"/>
+      <c r="L56" s="46"/>
+      <c r="M56" s="46"/>
+      <c r="N56" s="46"/>
+      <c r="O56" s="46"/>
+      <c r="P56" s="46"/>
+      <c r="Q56" s="46"/>
+      <c r="R56" s="46"/>
+      <c r="S56" s="46"/>
+      <c r="T56" s="46"/>
+      <c r="U56" s="46"/>
+      <c r="V56" s="46"/>
+      <c r="W56" s="46"/>
+      <c r="X56" s="46"/>
+      <c r="Y56" s="46"/>
+      <c r="Z56" s="46"/>
+      <c r="AA56" s="46"/>
+      <c r="AB56" s="46"/>
+      <c r="AC56" s="46"/>
+      <c r="AD56" s="46"/>
+      <c r="AE56" s="46"/>
+      <c r="AF56" s="46"/>
+      <c r="AG56" s="46"/>
+      <c r="AH56" s="46"/>
+      <c r="AI56" s="46"/>
+      <c r="AJ56" s="46"/>
+      <c r="AK56" s="46"/>
+      <c r="AL56" s="46"/>
+      <c r="AM56" s="46"/>
+      <c r="AN56" s="46"/>
+      <c r="AO56" s="46"/>
+      <c r="AP56" s="47"/>
       <c r="AQ56" s="1"/>
       <c r="AR56" s="1"/>
     </row>
-    <row r="57" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="40"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="40"/>
-      <c r="K57" s="40"/>
-      <c r="L57" s="40"/>
-      <c r="M57" s="40"/>
-      <c r="N57" s="40"/>
-      <c r="O57" s="40"/>
-      <c r="P57" s="40"/>
-      <c r="Q57" s="40"/>
-      <c r="R57" s="40"/>
-      <c r="S57" s="40"/>
-      <c r="T57" s="40"/>
-      <c r="U57" s="40"/>
-      <c r="V57" s="40"/>
-      <c r="W57" s="40"/>
-      <c r="X57" s="40"/>
-      <c r="Y57" s="40"/>
-      <c r="Z57" s="40"/>
-      <c r="AA57" s="40"/>
-      <c r="AB57" s="40"/>
-      <c r="AC57" s="40"/>
-      <c r="AD57" s="40"/>
-      <c r="AE57" s="40"/>
-      <c r="AF57" s="40"/>
-      <c r="AG57" s="40"/>
-      <c r="AH57" s="40"/>
-      <c r="AI57" s="40"/>
-      <c r="AJ57" s="40"/>
-      <c r="AK57" s="40"/>
-      <c r="AL57" s="40"/>
-      <c r="AM57" s="40"/>
-      <c r="AN57" s="40"/>
-      <c r="AO57" s="40"/>
-      <c r="AP57" s="40"/>
+    <row r="57" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="45"/>
+      <c r="B57" s="46"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="46"/>
+      <c r="H57" s="46"/>
+      <c r="I57" s="46"/>
+      <c r="J57" s="46"/>
+      <c r="K57" s="46"/>
+      <c r="L57" s="46"/>
+      <c r="M57" s="46"/>
+      <c r="N57" s="46"/>
+      <c r="O57" s="46"/>
+      <c r="P57" s="46"/>
+      <c r="Q57" s="46"/>
+      <c r="R57" s="46"/>
+      <c r="S57" s="46"/>
+      <c r="T57" s="46"/>
+      <c r="U57" s="46"/>
+      <c r="V57" s="46"/>
+      <c r="W57" s="46"/>
+      <c r="X57" s="46"/>
+      <c r="Y57" s="46"/>
+      <c r="Z57" s="46"/>
+      <c r="AA57" s="46"/>
+      <c r="AB57" s="46"/>
+      <c r="AC57" s="46"/>
+      <c r="AD57" s="46"/>
+      <c r="AE57" s="46"/>
+      <c r="AF57" s="46"/>
+      <c r="AG57" s="46"/>
+      <c r="AH57" s="46"/>
+      <c r="AI57" s="46"/>
+      <c r="AJ57" s="46"/>
+      <c r="AK57" s="46"/>
+      <c r="AL57" s="46"/>
+      <c r="AM57" s="46"/>
+      <c r="AN57" s="46"/>
+      <c r="AO57" s="46"/>
+      <c r="AP57" s="47"/>
       <c r="AQ57" s="1"/>
       <c r="AR57" s="1"/>
     </row>
-    <row r="58" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="40"/>
-      <c r="B58" s="40"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="40"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="40"/>
-      <c r="J58" s="40"/>
-      <c r="K58" s="40"/>
-      <c r="L58" s="40"/>
-      <c r="M58" s="40"/>
-      <c r="N58" s="40"/>
-      <c r="O58" s="40"/>
-      <c r="P58" s="40"/>
-      <c r="Q58" s="40"/>
-      <c r="R58" s="40"/>
-      <c r="S58" s="40"/>
-      <c r="T58" s="40"/>
-      <c r="U58" s="40"/>
-      <c r="V58" s="40"/>
-      <c r="W58" s="40"/>
-      <c r="X58" s="40"/>
-      <c r="Y58" s="40"/>
-      <c r="Z58" s="40"/>
-      <c r="AA58" s="40"/>
-      <c r="AB58" s="40"/>
-      <c r="AC58" s="40"/>
-      <c r="AD58" s="40"/>
-      <c r="AE58" s="40"/>
-      <c r="AF58" s="40"/>
-      <c r="AG58" s="40"/>
-      <c r="AH58" s="40"/>
-      <c r="AI58" s="40"/>
-      <c r="AJ58" s="40"/>
-      <c r="AK58" s="40"/>
-      <c r="AL58" s="40"/>
-      <c r="AM58" s="40"/>
-      <c r="AN58" s="40"/>
-      <c r="AO58" s="40"/>
-      <c r="AP58" s="40"/>
+    <row r="58" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="45"/>
+      <c r="B58" s="46"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="46"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="46"/>
+      <c r="K58" s="46"/>
+      <c r="L58" s="46"/>
+      <c r="M58" s="46"/>
+      <c r="N58" s="46"/>
+      <c r="O58" s="46"/>
+      <c r="P58" s="46"/>
+      <c r="Q58" s="46"/>
+      <c r="R58" s="46"/>
+      <c r="S58" s="46"/>
+      <c r="T58" s="46"/>
+      <c r="U58" s="46"/>
+      <c r="V58" s="46"/>
+      <c r="W58" s="46"/>
+      <c r="X58" s="46"/>
+      <c r="Y58" s="46"/>
+      <c r="Z58" s="46"/>
+      <c r="AA58" s="46"/>
+      <c r="AB58" s="46"/>
+      <c r="AC58" s="46"/>
+      <c r="AD58" s="46"/>
+      <c r="AE58" s="46"/>
+      <c r="AF58" s="46"/>
+      <c r="AG58" s="46"/>
+      <c r="AH58" s="46"/>
+      <c r="AI58" s="46"/>
+      <c r="AJ58" s="46"/>
+      <c r="AK58" s="46"/>
+      <c r="AL58" s="46"/>
+      <c r="AM58" s="46"/>
+      <c r="AN58" s="46"/>
+      <c r="AO58" s="46"/>
+      <c r="AP58" s="47"/>
       <c r="AQ58" s="1"/>
       <c r="AR58" s="1"/>
     </row>
-    <row r="59" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="40"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="40"/>
-      <c r="E59" s="40"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="40"/>
-      <c r="J59" s="40"/>
-      <c r="K59" s="40"/>
-      <c r="L59" s="40"/>
-      <c r="M59" s="40"/>
-      <c r="N59" s="40"/>
-      <c r="O59" s="40"/>
-      <c r="P59" s="40"/>
-      <c r="Q59" s="40"/>
-      <c r="R59" s="40"/>
-      <c r="S59" s="40"/>
-      <c r="T59" s="40"/>
-      <c r="U59" s="40"/>
-      <c r="V59" s="40"/>
-      <c r="W59" s="40"/>
-      <c r="X59" s="40"/>
-      <c r="Y59" s="40"/>
-      <c r="Z59" s="40"/>
-      <c r="AA59" s="40"/>
-      <c r="AB59" s="40"/>
-      <c r="AC59" s="40"/>
-      <c r="AD59" s="40"/>
-      <c r="AE59" s="40"/>
-      <c r="AF59" s="40"/>
-      <c r="AG59" s="40"/>
-      <c r="AH59" s="40"/>
-      <c r="AI59" s="40"/>
-      <c r="AJ59" s="40"/>
-      <c r="AK59" s="40"/>
-      <c r="AL59" s="40"/>
-      <c r="AM59" s="40"/>
-      <c r="AN59" s="40"/>
-      <c r="AO59" s="40"/>
-      <c r="AP59" s="40"/>
+    <row r="59" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="45"/>
+      <c r="B59" s="46"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="46"/>
+      <c r="G59" s="46"/>
+      <c r="H59" s="46"/>
+      <c r="I59" s="46"/>
+      <c r="J59" s="46"/>
+      <c r="K59" s="46"/>
+      <c r="L59" s="46"/>
+      <c r="M59" s="46"/>
+      <c r="N59" s="46"/>
+      <c r="O59" s="46"/>
+      <c r="P59" s="46"/>
+      <c r="Q59" s="46"/>
+      <c r="R59" s="46"/>
+      <c r="S59" s="46"/>
+      <c r="T59" s="46"/>
+      <c r="U59" s="46"/>
+      <c r="V59" s="46"/>
+      <c r="W59" s="46"/>
+      <c r="X59" s="46"/>
+      <c r="Y59" s="46"/>
+      <c r="Z59" s="46"/>
+      <c r="AA59" s="46"/>
+      <c r="AB59" s="46"/>
+      <c r="AC59" s="46"/>
+      <c r="AD59" s="46"/>
+      <c r="AE59" s="46"/>
+      <c r="AF59" s="46"/>
+      <c r="AG59" s="46"/>
+      <c r="AH59" s="46"/>
+      <c r="AI59" s="46"/>
+      <c r="AJ59" s="46"/>
+      <c r="AK59" s="46"/>
+      <c r="AL59" s="46"/>
+      <c r="AM59" s="46"/>
+      <c r="AN59" s="46"/>
+      <c r="AO59" s="46"/>
+      <c r="AP59" s="47"/>
       <c r="AQ59" s="1"/>
       <c r="AR59" s="1"/>
     </row>
-    <row r="60" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="40"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="40"/>
-      <c r="F60" s="40"/>
-      <c r="G60" s="40"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="40"/>
-      <c r="J60" s="40"/>
-      <c r="K60" s="40"/>
-      <c r="L60" s="40"/>
-      <c r="M60" s="40"/>
-      <c r="N60" s="40"/>
-      <c r="O60" s="40"/>
-      <c r="P60" s="40"/>
-      <c r="Q60" s="40"/>
-      <c r="R60" s="40"/>
-      <c r="S60" s="40"/>
-      <c r="T60" s="40"/>
-      <c r="U60" s="40"/>
-      <c r="V60" s="40"/>
-      <c r="W60" s="40"/>
-      <c r="X60" s="40"/>
-      <c r="Y60" s="40"/>
-      <c r="Z60" s="40"/>
-      <c r="AA60" s="40"/>
-      <c r="AB60" s="40"/>
-      <c r="AC60" s="40"/>
-      <c r="AD60" s="40"/>
-      <c r="AE60" s="40"/>
-      <c r="AF60" s="40"/>
-      <c r="AG60" s="40"/>
-      <c r="AH60" s="40"/>
-      <c r="AI60" s="40"/>
-      <c r="AJ60" s="40"/>
-      <c r="AK60" s="40"/>
-      <c r="AL60" s="40"/>
-      <c r="AM60" s="40"/>
-      <c r="AN60" s="40"/>
-      <c r="AO60" s="40"/>
-      <c r="AP60" s="40"/>
+    <row r="60" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="48"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="49"/>
+      <c r="J60" s="49"/>
+      <c r="K60" s="49"/>
+      <c r="L60" s="49"/>
+      <c r="M60" s="49"/>
+      <c r="N60" s="49"/>
+      <c r="O60" s="49"/>
+      <c r="P60" s="49"/>
+      <c r="Q60" s="49"/>
+      <c r="R60" s="49"/>
+      <c r="S60" s="49"/>
+      <c r="T60" s="49"/>
+      <c r="U60" s="49"/>
+      <c r="V60" s="49"/>
+      <c r="W60" s="49"/>
+      <c r="X60" s="49"/>
+      <c r="Y60" s="49"/>
+      <c r="Z60" s="49"/>
+      <c r="AA60" s="49"/>
+      <c r="AB60" s="49"/>
+      <c r="AC60" s="49"/>
+      <c r="AD60" s="49"/>
+      <c r="AE60" s="49"/>
+      <c r="AF60" s="49"/>
+      <c r="AG60" s="49"/>
+      <c r="AH60" s="49"/>
+      <c r="AI60" s="49"/>
+      <c r="AJ60" s="49"/>
+      <c r="AK60" s="49"/>
+      <c r="AL60" s="49"/>
+      <c r="AM60" s="49"/>
+      <c r="AN60" s="49"/>
+      <c r="AO60" s="49"/>
+      <c r="AP60" s="50"/>
       <c r="AQ60" s="1"/>
       <c r="AR60" s="1"/>
     </row>
-    <row r="61" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="6" t="s">
         <v>30</v>
       </c>
@@ -5398,7 +4303,7 @@
       <c r="AQ61" s="1"/>
       <c r="AR61" s="1"/>
     </row>
-    <row r="62" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -5444,7 +4349,7 @@
       <c r="AQ62" s="1"/>
       <c r="AR62" s="1"/>
     </row>
-    <row r="63" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="9"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
@@ -5491,7 +4396,7 @@
       <c r="AR63" s="1"/>
       <c r="AS63" s="3"/>
     </row>
-    <row r="64" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="12"/>
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
@@ -5537,7 +4442,7 @@
       <c r="AQ64" s="1"/>
       <c r="AR64" s="1"/>
     </row>
-    <row r="65" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="12"/>
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
@@ -5584,7 +4489,7 @@
       <c r="AR65" s="1"/>
       <c r="AS65" s="4"/>
     </row>
-    <row r="66" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="12"/>
       <c r="B66" s="13"/>
       <c r="C66" s="13"/>
@@ -5631,7 +4536,7 @@
       <c r="AR66" s="1"/>
       <c r="AS66" s="3"/>
     </row>
-    <row r="67" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="12"/>
       <c r="B67" s="13"/>
       <c r="C67" s="13"/>
@@ -5677,7 +4582,7 @@
       <c r="AQ67" s="1"/>
       <c r="AR67" s="1"/>
     </row>
-    <row r="68" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="12"/>
       <c r="B68" s="13"/>
       <c r="C68" s="13"/>
@@ -5723,7 +4628,7 @@
       <c r="AQ68" s="1"/>
       <c r="AR68" s="1"/>
     </row>
-    <row r="69" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="12"/>
       <c r="B69" s="13"/>
       <c r="C69" s="13"/>
@@ -5769,7 +4674,7 @@
       <c r="AQ69" s="1"/>
       <c r="AR69" s="1"/>
     </row>
-    <row r="70" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="12"/>
       <c r="B70" s="13"/>
       <c r="C70" s="13"/>
@@ -5815,7 +4720,7 @@
       <c r="AQ70" s="1"/>
       <c r="AR70" s="1"/>
     </row>
-    <row r="71" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="12"/>
       <c r="B71" s="13"/>
       <c r="C71" s="13"/>
@@ -5861,7 +4766,7 @@
       <c r="AQ71" s="1"/>
       <c r="AR71" s="1"/>
     </row>
-    <row r="72" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="15"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -5907,7 +4812,7 @@
       <c r="AQ72" s="1"/>
       <c r="AR72" s="1"/>
     </row>
-    <row r="73" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -5953,7 +4858,7 @@
       <c r="AQ73" s="1"/>
       <c r="AR73" s="1"/>
     </row>
-    <row r="74" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -5999,7 +4904,7 @@
       <c r="AQ74" s="1"/>
       <c r="AR74" s="1"/>
     </row>
-    <row r="75" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -6045,7 +4950,7 @@
       <c r="AQ75" s="1"/>
       <c r="AR75" s="1"/>
     </row>
-    <row r="76" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -6091,7 +4996,7 @@
       <c r="AQ76" s="1"/>
       <c r="AR76" s="1"/>
     </row>
-    <row r="77" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -6137,586 +5042,586 @@
       <c r="AQ77" s="1"/>
       <c r="AR77" s="1"/>
     </row>
-    <row r="78" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="79" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="80" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="81" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="82" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="83" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="84" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="85" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="86" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="87" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="88" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="89" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="90" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="91" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="92" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="93" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="94" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="95" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="96" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="97" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="98" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="99" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="100" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="101" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="102" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="103" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="104" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="105" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="106" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="107" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="108" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="109" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="110" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="111" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="112" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="113" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="114" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="115" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="116" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="117" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="118" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="119" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="120" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="121" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="122" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="123" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="124" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="125" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="126" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="127" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="128" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="129" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="130" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="131" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="132" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="133" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="134" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="135" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="136" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="137" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="138" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="139" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="140" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="141" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="142" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="143" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="144" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="145" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="146" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="147" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="148" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="149" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="150" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="151" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="152" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="153" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="154" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="155" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="156" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="157" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="158" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="159" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="160" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="161" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="162" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="163" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="164" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="165" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="166" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="167" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="168" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="169" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="170" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="171" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="172" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="173" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="174" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="175" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="176" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="177" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="178" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="179" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="180" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="181" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="182" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="183" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="184" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="185" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="186" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="187" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="188" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="189" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="190" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="191" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="192" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="193" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="194" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="195" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="196" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="197" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="198" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="199" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="200" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="201" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="202" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="203" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="204" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="205" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="206" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="207" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="208" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="209" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="210" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="211" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="212" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="213" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="214" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="215" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="216" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="217" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="218" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="219" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="220" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="221" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="222" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="223" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="224" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="225" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="226" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="227" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="228" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="229" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="230" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="231" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="232" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="233" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="234" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="235" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="236" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="237" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="238" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="239" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="240" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="241" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="242" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="243" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="244" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="245" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="246" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="247" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="248" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="249" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="250" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="251" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="252" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="253" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="254" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="255" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="256" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="257" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="258" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="259" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="260" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="261" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="262" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="263" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="264" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="265" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="266" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="267" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="268" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="269" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="270" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="271" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="272" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="273" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="274" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="275" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="276" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="277" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="278" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="279" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="280" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="281" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="282" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="283" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="284" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="285" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="286" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="287" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="288" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="289" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="290" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="291" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="292" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="293" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="294" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="295" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="296" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="297" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="298" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="299" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="300" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="301" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="302" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="303" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="304" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="305" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="306" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="307" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="308" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="309" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="310" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="311" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="312" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="313" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="314" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="315" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="316" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="317" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="318" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="319" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="320" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="321" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="322" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="323" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="324" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="325" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="326" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="327" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="328" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="329" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="330" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="331" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="332" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="333" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="334" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="335" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="336" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="337" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="338" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="339" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="340" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="341" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="342" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="343" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="344" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="345" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="346" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="347" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="348" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="349" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="350" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="351" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="352" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="353" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="354" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="355" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="356" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="357" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="358" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="359" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="360" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="361" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="362" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="363" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="364" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="365" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="366" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="367" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="368" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="369" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="370" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="371" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="372" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="373" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="374" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="375" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="376" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="377" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="378" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="379" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="380" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="381" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="382" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="383" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="384" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="385" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="386" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="387" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="388" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="389" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="390" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="391" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="392" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="393" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="394" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="395" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="396" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="397" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="398" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="399" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="400" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="401" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="402" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="403" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="404" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="405" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="406" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="407" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="408" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="409" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="410" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="411" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="412" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="413" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="414" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="415" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="416" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="417" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="418" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="419" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="420" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="421" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="422" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="423" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="424" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="425" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="426" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="427" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="428" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="429" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="430" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="431" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="432" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="433" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="434" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="435" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="436" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="437" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="438" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="439" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="440" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="441" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="442" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="443" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="444" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="445" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="446" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="447" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="448" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="449" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="450" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="451" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="452" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="453" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="454" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="455" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="456" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="457" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="458" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="459" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="460" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="461" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="462" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="463" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="464" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="465" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="466" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="467" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="468" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="469" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="470" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="471" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="472" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="473" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="474" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="475" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="476" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="477" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="478" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="479" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="480" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="481" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="482" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="483" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="484" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="485" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="486" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="487" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="488" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="489" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="490" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="491" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="492" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="493" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="494" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="495" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="496" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="497" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="498" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="499" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="500" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="501" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="502" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="503" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="504" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="505" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="506" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="507" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="508" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="509" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="510" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="511" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="512" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="513" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="514" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="515" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="516" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="517" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="518" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="519" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="520" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="521" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="522" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="523" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="524" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="525" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="526" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="527" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="528" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="529" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="530" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="531" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="532" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="533" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="534" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="535" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="536" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="537" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="538" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="539" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="540" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="541" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="542" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="543" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="544" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="545" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="546" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="547" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="548" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="549" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="550" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="551" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="552" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="553" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="554" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="555" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="556" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="557" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="558" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="559" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="560" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="561" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="562" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="563" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="564" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="565" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="566" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="567" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="568" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="569" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="570" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="571" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="572" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="573" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="574" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="575" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="576" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="577" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="578" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="579" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="580" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="581" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="582" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="583" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="584" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="585" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="586" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="587" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="588" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="589" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="590" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="591" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="592" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="593" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="594" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="595" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="596" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="597" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="598" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="599" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="600" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="601" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="602" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="603" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="604" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="605" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="606" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="607" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="608" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="609" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="610" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="611" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="612" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="613" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="614" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="615" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="616" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="617" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="618" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="619" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="620" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="621" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="622" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="623" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="624" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="625" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="626" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="627" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="628" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="629" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="630" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="631" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="632" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="633" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="634" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="635" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="636" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="637" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="638" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="639" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="640" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="641" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="642" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="643" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="644" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="645" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="646" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="647" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="648" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="649" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="650" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="651" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="652" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="653" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="654" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="655" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="656" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="657" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="78" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="79" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="80" spans="1:45" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="81" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="82" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="83" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="84" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="85" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="86" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="87" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="88" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="89" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="90" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="91" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="92" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="93" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="94" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="95" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="96" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="97" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="98" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="99" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="100" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="101" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="102" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="103" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="104" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="105" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="106" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="107" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="108" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="109" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="110" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="111" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="112" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="113" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="114" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="115" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="116" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="117" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="118" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="119" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="120" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="121" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="122" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="123" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="124" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="125" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="126" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="127" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="128" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="129" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="130" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="131" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="132" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="133" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="134" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="135" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="136" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="137" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="138" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="139" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="140" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="141" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="142" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="143" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="144" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="145" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="146" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="147" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="148" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="149" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="150" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="151" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="152" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="153" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="154" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="155" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="156" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="157" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="158" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="159" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="160" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="161" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="162" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="163" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="164" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="165" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="166" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="167" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="168" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="169" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="170" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="171" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="172" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="173" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="174" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="175" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="176" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="177" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="178" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="179" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="180" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="181" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="182" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="183" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="184" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="185" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="186" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="187" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="188" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="189" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="190" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="191" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="192" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="193" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="194" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="195" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="196" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="197" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="198" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="199" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="200" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="201" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="202" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="203" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="204" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="205" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="206" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="207" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="208" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="209" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="210" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="211" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="212" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="213" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="214" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="215" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="216" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="217" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="218" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="219" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="220" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="221" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="222" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="223" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="224" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="225" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="226" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="227" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="228" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="229" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="230" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="231" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="232" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="233" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="234" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="235" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="236" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="237" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="238" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="239" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="240" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="241" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="242" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="243" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="244" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="245" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="246" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="247" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="248" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="249" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="250" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="251" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="252" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="253" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="254" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="255" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="256" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="257" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="258" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="259" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="260" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="261" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="262" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="263" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="264" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="265" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="266" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="267" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="268" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="269" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="270" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="271" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="272" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="273" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="274" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="275" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="276" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="277" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="278" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="279" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="280" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="281" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="282" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="283" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="284" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="285" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="286" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="287" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="288" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="289" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="290" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="291" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="292" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="293" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="294" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="295" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="296" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="297" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="298" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="299" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="300" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="301" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="302" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="303" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="304" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="305" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="306" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="307" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="308" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="309" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="310" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="311" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="312" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="313" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="314" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="315" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="316" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="317" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="318" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="319" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="320" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="321" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="322" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="323" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="324" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="325" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="326" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="327" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="328" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="329" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="330" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="331" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="332" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="333" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="334" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="335" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="336" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="337" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="338" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="339" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="340" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="341" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="342" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="343" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="344" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="345" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="346" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="347" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="348" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="349" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="350" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="351" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="352" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="353" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="354" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="355" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="356" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="357" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="358" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="359" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="360" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="361" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="362" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="363" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="364" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="365" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="366" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="367" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="368" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="369" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="370" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="371" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="372" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="373" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="374" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="375" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="376" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="377" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="378" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="379" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="380" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="381" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="382" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="383" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="384" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="385" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="386" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="387" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="388" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="389" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="390" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="391" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="392" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="393" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="394" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="395" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="396" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="397" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="398" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="399" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="400" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="401" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="402" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="403" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="404" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="405" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="406" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="407" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="408" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="409" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="410" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="411" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="412" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="413" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="414" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="415" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="416" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="417" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="418" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="419" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="420" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="421" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="422" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="423" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="424" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="425" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="426" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="427" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="428" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="429" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="430" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="431" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="432" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="433" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="434" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="435" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="436" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="437" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="438" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="439" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="440" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="441" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="442" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="443" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="444" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="445" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="446" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="447" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="448" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="449" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="450" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="451" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="452" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="453" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="454" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="455" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="456" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="457" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="458" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="459" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="460" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="461" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="462" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="463" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="464" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="465" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="466" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="467" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="468" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="469" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="470" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="471" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="472" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="473" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="474" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="475" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="476" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="477" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="478" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="479" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="480" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="481" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="482" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="483" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="484" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="485" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="486" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="487" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="488" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="489" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="490" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="491" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="492" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="493" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="494" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="495" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="496" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="497" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="498" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="499" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="500" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="501" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="502" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="503" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="504" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="505" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="506" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="507" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="508" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="509" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="510" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="511" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="512" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="513" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="514" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="515" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="516" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="517" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="518" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="519" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="520" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="521" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="522" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="523" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="524" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="525" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="526" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="527" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="528" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="529" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="530" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="531" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="532" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="533" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="534" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="535" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="536" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="537" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="538" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="539" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="540" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="541" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="542" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="543" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="544" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="545" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="546" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="547" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="548" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="549" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="550" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="551" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="552" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="553" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="554" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="555" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="556" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="557" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="558" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="559" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="560" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="561" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="562" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="563" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="564" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="565" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="566" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="567" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="568" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="569" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="570" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="571" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="572" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="573" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="574" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="575" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="576" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="577" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="578" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="579" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="580" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="581" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="582" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="583" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="584" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="585" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="586" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="587" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="588" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="589" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="590" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="591" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="592" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="593" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="594" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="595" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="596" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="597" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="598" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="599" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="600" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="601" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="602" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="603" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="604" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="605" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="606" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="607" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="608" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="609" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="610" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="611" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="612" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="613" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="614" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="615" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="616" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="617" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="618" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="619" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="620" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="621" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="622" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="623" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="624" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="625" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="626" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="627" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="628" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="629" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="630" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="631" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="632" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="633" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="634" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="635" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="636" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="637" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="638" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="639" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="640" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="641" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="642" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="643" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="644" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="645" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="646" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="647" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="648" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="649" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="650" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="651" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="652" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="653" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="654" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="655" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="656" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="657" ht="10.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="79">
     <mergeCell ref="AF3:AM3"/>
@@ -6807,299 +5712,5 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1026" r:id="rId4" name="Check Box 2">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>31750</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>57150</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1028" r:id="rId5" name="Check Box 4">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>50800</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1029" r:id="rId6" name="Check Box 5">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>30</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>32</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1030" r:id="rId7" name="Check Box 6">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>33</xdr:col>
-                    <xdr:colOff>107950</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>34</xdr:col>
-                    <xdr:colOff>146050</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1031" r:id="rId8" name="Check Box 7">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>36</xdr:col>
-                    <xdr:colOff>95250</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>38</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1034" r:id="rId9" name="Check Box 10">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>57150</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>88900</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1035" r:id="rId10" name="Check Box 11">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>25</xdr:col>
-                    <xdr:colOff>88900</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>26</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1036" r:id="rId11" name="Check Box 12">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>12</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>13</xdr:col>
-                    <xdr:colOff>31750</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1037" r:id="rId12" name="Check Box 13">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>76200</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>9</xdr:col>
-                    <xdr:colOff>107950</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1038" r:id="rId13" name="Check Box 14">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>21</xdr:col>
-                    <xdr:colOff>88900</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>22</xdr:col>
-                    <xdr:colOff>114300</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1039" r:id="rId14" name="Check Box 15">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>16</xdr:col>
-                    <xdr:colOff>31750</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>17</xdr:col>
-                    <xdr:colOff>57150</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1040" r:id="rId15" name="Check Box 16">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>30</xdr:col>
-                    <xdr:colOff>12700</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>31</xdr:col>
-                    <xdr:colOff>38100</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1041" r:id="rId16" name="Check Box 17">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>34</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>35</xdr:col>
-                    <xdr:colOff>50800</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>69850</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
 </worksheet>
 </file>